--- a/admission_log.xlsx
+++ b/admission_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,6 +571,86 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-21 04:35:08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Blessings Chirwa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mandindip@mchs.adventist.org</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bachelor of Science</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Connection unexpectedly closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-21 04:36:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pemphero Mandindi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mandindip@mchs.adventist.org</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bachelor of Arts</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
